--- a/files/港岛-筲箕湾-One Eighty.xlsx
+++ b/files/港岛-筲箕湾-One Eighty.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="One Eighty 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="One Eighty" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,13 +237,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -3308,259 +3346,259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Eighty - One Eighty 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>One Eighty 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>57 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>16 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>41 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 332呎 (2房)
-$1,460万
+$1460万
 $43,975/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 332呎 (2房)
-$1,369万
+$1369万
 $41,235/呎
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 331呎 (2房)
-$1,090万
+$1090万
 $32,917/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 332呎 (2房)
-$1,093万
+$1093万
 $32,915/呎
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 331呎 (2房)
-$1,071万
+$1071万
 $32,349/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 332呎 (2房)
-$1,074万
+$1074万
 $32,349/呎
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 332呎 (2房)
-$1,052万
+$1052万
 $31,685/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 333呎 (2房)
-$1,055万
+$1055万
 $31,684/呎
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 332呎 (2房)
-$1,033万
+$1033万
 $31,118/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 333呎 (2房)
-$1,036万
+$1036万
 $31,119/呎
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 332呎 (2房)
-$1,014万
+$1014万
 $30,552/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 332呎 (2房)
-$1,017万
+$1017万
 $30,646/呎
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 331呎 (2房)
 $859万
@@ -3568,7 +3606,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 333呎 (2房)
 $999万
@@ -3576,15 +3614,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 331呎 (2房)
 $843万
@@ -3592,7 +3630,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 333呎 (2房)
 $980万
@@ -3600,15 +3638,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $660万
@@ -3616,7 +3654,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 165呎 (开放式)
 $436万
@@ -3624,7 +3662,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $645万
@@ -3633,13 +3671,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $633万
@@ -3647,7 +3685,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 164呎 (开放式)
 $418万
@@ -3655,7 +3693,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $618万
@@ -3664,13 +3702,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $643万
@@ -3678,7 +3716,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 164呎 (开放式)
 $425万
@@ -3686,7 +3724,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $627万
@@ -3695,13 +3733,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $618万
@@ -3709,7 +3747,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 165呎 (开放式)
 $399万
@@ -3717,7 +3755,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $612万
@@ -3726,13 +3764,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $596万
@@ -3740,7 +3778,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 164呎 (开放式)
 $394万
@@ -3748,7 +3786,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $586万
@@ -3757,13 +3795,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $591万
@@ -3771,7 +3809,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 165呎 (开放式)
 $389万
@@ -3779,7 +3817,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $578万
@@ -3788,13 +3826,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $614万
@@ -3802,7 +3840,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 165呎 (开放式)
 $403万
@@ -3810,7 +3848,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $599万
@@ -3819,13 +3857,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $577万
@@ -3833,7 +3871,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 164呎 (开放式)
 $379万
@@ -3841,7 +3879,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $563万
@@ -3850,13 +3888,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $569万
@@ -3864,7 +3902,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 164呎 (开放式)
 $373万
@@ -3872,7 +3910,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $555万
@@ -3881,13 +3919,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $589万
@@ -3895,7 +3933,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 164呎 (开放式)
 $368万
@@ -3903,7 +3941,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 247呎 (1房)
 $575万
@@ -3912,13 +3950,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $580万
@@ -3926,7 +3964,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 165呎 (开放式)
 $381万
@@ -3934,7 +3972,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $544万
@@ -3943,13 +3981,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $545万
@@ -3957,7 +3995,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 165呎 (开放式)
 $358万
@@ -3965,7 +4003,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $511万
@@ -3974,13 +4012,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 253呎 (1房)
 $536万
@@ -3988,7 +4026,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 164呎 (开放式)
 $353万
@@ -3996,7 +4034,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 248呎 (1房)
 $503万
@@ -4005,33 +4043,33 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 323呎 (1房)
-$1,082万
+$1082万
 $33,506/呎
 (在售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 324呎 (1房)
-$1,095万
+$1095万
 $33,792/呎
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr"/>
+      <c r="D26" s="21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/港岛-筲箕湾-One Eighty.xlsx
+++ b/files/港岛-筲箕湾-One Eighty.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -644,10 +644,14 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -705,6 +709,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -751,6 +775,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>11636415</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>35049</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -797,6 +837,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>12409830</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>37379</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -843,6 +899,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>9288672</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>27978</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -889,6 +961,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>9261218</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>27980</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -935,6 +1023,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>9128788</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>27496</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -981,6 +1085,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>9101332</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>27496</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1027,6 +1147,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>8968095</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>26931</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1073,6 +1209,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>8941448</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>26932</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1119,6 +1271,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>8808210</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>26451</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1165,6 +1333,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>8781562</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>26450</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1211,6 +1395,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>8648325</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>26049</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1257,6 +1457,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>8621678</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>25969</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1303,6 +1519,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>8487632</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>25488</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1338,7 +1570,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1349,6 +1581,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7304560</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>22068</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1395,6 +1643,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>8327748</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>25008</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1430,7 +1694,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1441,6 +1705,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7166520</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>21651</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1476,7 +1756,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-11</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1487,6 +1767,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>5478420</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>22180</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1522,7 +1818,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1533,6 +1829,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>3705915</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>22460</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1568,7 +1880,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1579,6 +1891,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>5609405</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>22172</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1614,7 +1942,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1625,6 +1953,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>5253255</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>21182</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1660,7 +2004,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1671,6 +2015,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>3553935</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>21670</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1706,7 +2066,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1717,6 +2077,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5378715</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>21260</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1752,7 +2128,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1763,6 +2139,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>5327800</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>21483</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1798,7 +2190,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-24</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1809,6 +2201,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>3615985</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>22049</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1844,7 +2252,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1855,6 +2263,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>5464480</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>21599</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1890,7 +2314,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1901,6 +2325,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>5199620</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>21051</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1936,7 +2376,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1947,6 +2387,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>3392265</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>20559</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1982,7 +2438,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1993,6 +2449,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>5251895</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>20758</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2028,7 +2500,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2039,6 +2511,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>4981425</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>20086</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2074,7 +2562,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2085,6 +2573,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>3349085</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>20421</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2120,7 +2624,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2131,6 +2635,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>5062260</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>20009</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2166,7 +2686,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2177,6 +2697,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>4915890</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>19902</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2212,7 +2748,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2223,6 +2759,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>3305140</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>20031</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2258,7 +2810,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2269,6 +2821,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>5023925</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>19857</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2304,7 +2872,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2315,6 +2883,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>5092265</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>20533</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2350,7 +2934,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2361,6 +2945,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>3424395</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>20754</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2396,7 +2996,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2407,6 +3007,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>5216280</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>20618</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2442,7 +3058,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2453,6 +3069,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>4784140</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>19369</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2488,7 +3120,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2499,6 +3131,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>3217335</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>19618</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2534,7 +3182,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-24</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2545,6 +3193,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>4901270</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>19373</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2580,7 +3244,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-24</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2591,6 +3255,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>4717925</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>19101</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2626,7 +3306,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-24</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2637,6 +3317,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>3174070</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>19354</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2672,7 +3368,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-24</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2683,6 +3379,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>4832930</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>19102</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2718,7 +3430,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-24</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2729,6 +3441,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>4885205</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>19778</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2764,7 +3492,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2775,6 +3503,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>3130210</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>19087</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2810,7 +3554,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2821,6 +3565,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>5003695</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>19777</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2856,7 +3616,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-24</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2867,6 +3627,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>4623150</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>18642</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2902,7 +3678,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2913,6 +3689,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>3241050</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>19643</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2948,7 +3740,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-20</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2959,6 +3751,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>4932635</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>19497</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2994,7 +3802,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3005,6 +3813,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>4340185</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>17501</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3040,7 +3864,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3051,6 +3875,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>3042405</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>18439</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3086,7 +3926,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3097,6 +3937,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>4630800</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>18304</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3132,7 +3988,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3143,6 +3999,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>4272610</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>17228</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3178,7 +4050,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-24</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3189,6 +4061,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>2999140</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>18287</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3224,7 +4112,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3235,6 +4123,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>4559060</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>18020</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3281,6 +4185,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>9306225</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>28723</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3327,13 +4247,29 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>9199125</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>28480</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -3603,7 +4539,7 @@
           <t>A | 331呎 (2房)
 $859万
 $25,963/呎
-(已售)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -3627,7 +4563,7 @@
           <t>A | 331呎 (2房)
 $843万
 $25,472/呎
-(已售)</t>
+(20年-06月-17日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -3651,7 +4587,7 @@
           <t>A | 253呎 (1房)
 $660万
 $26,084/呎
-(已售)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -3659,7 +4595,7 @@
           <t>B | 165呎 (开放式)
 $436万
 $26,424/呎
-(已售)</t>
+(19年-11月-28日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -3667,7 +4603,7 @@
           <t>C | 247呎 (1房)
 $645万
 $26,094/呎
-(已售)</t>
+(20年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -3682,7 +4618,7 @@
           <t>A | 253呎 (1房)
 $633万
 $25,011/呎
-(已售)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -3690,7 +4626,7 @@
           <t>B | 164呎 (开放式)
 $418万
 $25,495/呎
-(已售)</t>
+(19年-11月-28日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -3698,7 +4634,7 @@
           <t>C | 248呎 (1房)
 $618万
 $24,921/呎
-(已售)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -3713,7 +4649,7 @@
           <t>A | 253呎 (1房)
 $643万
 $25,410/呎
-(已售)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -3721,7 +4657,7 @@
           <t>B | 164呎 (开放式)
 $425万
 $25,940/呎
-(已售)</t>
+(19年-11月-24日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -3729,7 +4665,7 @@
           <t>C | 248呎 (1房)
 $627万
 $25,274/呎
-(已售)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -3744,7 +4680,7 @@
           <t>A | 253呎 (1房)
 $618万
 $24,422/呎
-(已售)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -3752,7 +4688,7 @@
           <t>B | 165呎 (开放式)
 $399万
 $24,187/呎
-(已售)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -3760,7 +4696,7 @@
           <t>C | 247呎 (1房)
 $612万
 $24,766/呎
-(已售)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -3775,7 +4711,7 @@
           <t>A | 253呎 (1房)
 $596万
 $23,540/呎
-(已售)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -3783,7 +4719,7 @@
           <t>B | 164呎 (开放式)
 $394万
 $24,025/呎
-(已售)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -3791,7 +4727,7 @@
           <t>C | 248呎 (1房)
 $586万
 $23,631/呎
-(已售)</t>
+(19年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -3806,7 +4742,7 @@
           <t>A | 253呎 (1房)
 $591万
 $23,362/呎
-(已售)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -3814,7 +4750,7 @@
           <t>B | 165呎 (开放式)
 $389万
 $23,566/呎
-(已售)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -3822,7 +4758,7 @@
           <t>C | 247呎 (1房)
 $578万
 $23,415/呎
-(已售)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -3837,7 +4773,7 @@
           <t>A | 253呎 (1房)
 $614万
 $24,256/呎
-(已售)</t>
+(19年-11月-28日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -3845,7 +4781,7 @@
           <t>B | 165呎 (开放式)
 $403万
 $24,416/呎
-(已售)</t>
+(20年-07月-02日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -3853,7 +4789,7 @@
           <t>C | 248呎 (1房)
 $599万
 $24,157/呎
-(已售)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -3868,7 +4804,7 @@
           <t>A | 253呎 (1房)
 $577万
 $22,791/呎
-(已售)</t>
+(19年-11月-24日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -3876,7 +4812,7 @@
           <t>B | 164呎 (开放式)
 $379万
 $23,080/呎
-(已售)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -3884,7 +4820,7 @@
           <t>C | 247呎 (1房)
 $563万
 $22,787/呎
-(已售)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -3899,7 +4835,7 @@
           <t>A | 253呎 (1房)
 $569万
 $22,474/呎
-(已售)</t>
+(19年-11月-24日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -3907,7 +4843,7 @@
           <t>B | 164呎 (开放式)
 $373万
 $22,770/呎
-(已售)</t>
+(19年-11月-24日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -3915,7 +4851,7 @@
           <t>C | 247呎 (1房)
 $555万
 $22,472/呎
-(已售)</t>
+(19年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -3930,7 +4866,7 @@
           <t>A | 253呎 (1房)
 $589万
 $23,268/呎
-(已售)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -3938,7 +4874,7 @@
           <t>B | 164呎 (开放式)
 $368万
 $22,455/呎
-(已售)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -3946,7 +4882,7 @@
           <t>C | 247呎 (1房)
 $575万
 $23,268/呎
-(已售)</t>
+(19年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -3961,7 +4897,7 @@
           <t>A | 253呎 (1房)
 $580万
 $22,937/呎
-(已售)</t>
+(19年-11月-20日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -3969,7 +4905,7 @@
           <t>B | 165呎 (开放式)
 $381万
 $23,109/呎
-(已售)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -3977,7 +4913,7 @@
           <t>C | 248呎 (1房)
 $544万
 $21,931/呎
-(已售)</t>
+(19年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4928,7 @@
           <t>A | 253呎 (1房)
 $545万
 $21,534/呎
-(已售)</t>
+(19年-11月-21日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -4000,7 +4936,7 @@
           <t>B | 165呎 (开放式)
 $358万
 $21,693/呎
-(已售)</t>
+(19年-11月-21日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -4008,7 +4944,7 @@
           <t>C | 248呎 (1房)
 $511万
 $20,589/呎
-(已售)</t>
+(19年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4959,7 @@
           <t>A | 253呎 (1房)
 $536万
 $21,200/呎
-(已售)</t>
+(19年-11月-21日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -4031,7 +4967,7 @@
           <t>B | 164呎 (开放式)
 $353万
 $21,515/呎
-(已售)</t>
+(19年-11月-24日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -4039,7 +4975,7 @@
           <t>C | 248呎 (1房)
 $503万
 $20,269/呎
-(已售)</t>
+(19年-11月-21日)</t>
         </is>
       </c>
     </row>
